--- a/Library/Library_Data/Books_Data.xlsx
+++ b/Library/Library_Data/Books_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\training\Python\Library\Library_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8D7041-DF99-4BFB-9ADC-FF49FBDAE22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BAF6B0-907B-4EDB-900C-666FF0B7ECEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mythology" sheetId="1" r:id="rId1"/>
@@ -49,6 +49,18 @@
     <t>Published Date</t>
   </si>
   <si>
+    <t>Market Price (INR)</t>
+  </si>
+  <si>
+    <t>Quantities Available</t>
+  </si>
+  <si>
+    <t>Charges per day (Rs)</t>
+  </si>
+  <si>
+    <t>MYTH10001</t>
+  </si>
+  <si>
     <t>The Palace of Illusions</t>
   </si>
   <si>
@@ -61,6 +73,9 @@
     <t>12-02-2008</t>
   </si>
   <si>
+    <t>MYTH10002</t>
+  </si>
+  <si>
     <t>The Immortals of Meluha</t>
   </si>
   <si>
@@ -70,6 +85,9 @@
     <t>01-02-2010</t>
   </si>
   <si>
+    <t>MYTH10003</t>
+  </si>
+  <si>
     <t>Asura: Tale of the Vanquished</t>
   </si>
   <si>
@@ -79,6 +97,9 @@
     <t>14-05-2012</t>
   </si>
   <si>
+    <t>MYTH10004</t>
+  </si>
+  <si>
     <t>The Pregnant King</t>
   </si>
   <si>
@@ -88,42 +109,63 @@
     <t>14-02-2008</t>
   </si>
   <si>
+    <t>MYTH10005</t>
+  </si>
+  <si>
     <t>Shiva to Shankara</t>
   </si>
   <si>
     <t>01-01-2006</t>
   </si>
   <si>
+    <t>MYTH10006</t>
+  </si>
+  <si>
     <t>The Secret of the Nagas</t>
   </si>
   <si>
     <t>01-08-2011</t>
   </si>
   <si>
+    <t>MYTH10007</t>
+  </si>
+  <si>
     <t>The Oath of the Vayuputras</t>
   </si>
   <si>
     <t>27-02-2013</t>
   </si>
   <si>
+    <t>MYTH10008</t>
+  </si>
+  <si>
     <t>Jaya: An Illustrated Retelling of the Mahabharata</t>
   </si>
   <si>
     <t>14-08-2010</t>
   </si>
   <si>
+    <t>MYTH10009</t>
+  </si>
+  <si>
     <t>Sita: An Illustrated Retelling of the Ramayana</t>
   </si>
   <si>
     <t>01-10-2013</t>
   </si>
   <si>
+    <t>MYTH10010</t>
+  </si>
+  <si>
     <t>Lanka's Princess</t>
   </si>
   <si>
     <t>01-12-2016</t>
   </si>
   <si>
+    <t>CRIMYS10001</t>
+  </si>
+  <si>
     <t>The Rozabal Line</t>
   </si>
   <si>
@@ -133,48 +175,72 @@
     <t>01-01-2007</t>
   </si>
   <si>
+    <t>CRIMYS10002</t>
+  </si>
+  <si>
     <t>Sacred Games</t>
   </si>
   <si>
     <t>Vikram Chandra</t>
   </si>
   <si>
+    <t>CRIMYS10003</t>
+  </si>
+  <si>
     <t>The Krishna Key</t>
   </si>
   <si>
     <t>01-08-2012</t>
   </si>
   <si>
+    <t>CRIMYS10004</t>
+  </si>
+  <si>
     <t>The Sialkot Saga</t>
   </si>
   <si>
     <t>01-08-2016</t>
   </si>
   <si>
+    <t>CRIMYS10005</t>
+  </si>
+  <si>
     <t>Chanakya's Chant</t>
   </si>
   <si>
     <t>01-01-2010</t>
   </si>
   <si>
+    <t>CRIMYS10006</t>
+  </si>
+  <si>
     <t>The Keepers of the Kalachakra</t>
   </si>
   <si>
     <t>01-01-2018</t>
   </si>
   <si>
+    <t>CRIMYS10007</t>
+  </si>
+  <si>
     <t>The Vault of Vishnu</t>
   </si>
   <si>
     <t>27-01-2020</t>
   </si>
   <si>
+    <t>CRIMYS10008</t>
+  </si>
+  <si>
     <t>The Magicians of Mazda</t>
   </si>
   <si>
     <t>21-05-2022</t>
   </si>
   <si>
+    <t>CRIMYS10009</t>
+  </si>
+  <si>
     <t>The Night Express</t>
   </si>
   <si>
@@ -184,6 +250,9 @@
     <t>01-01-2012</t>
   </si>
   <si>
+    <t>CRIMYS10010</t>
+  </si>
+  <si>
     <t>The Tokyo Conspiracy</t>
   </si>
   <si>
@@ -193,6 +262,9 @@
     <t>01-01-2015</t>
   </si>
   <si>
+    <t>ROMNC10001</t>
+  </si>
+  <si>
     <t>2 States</t>
   </si>
   <si>
@@ -202,6 +274,9 @@
     <t>01-10-2009</t>
   </si>
   <si>
+    <t>ROMNC10002</t>
+  </si>
+  <si>
     <t>I Too Had a Love Story</t>
   </si>
   <si>
@@ -211,6 +286,9 @@
     <t>28-02-2007</t>
   </si>
   <si>
+    <t>ROMNC10003</t>
+  </si>
+  <si>
     <t>Wish I Could Tell You</t>
   </si>
   <si>
@@ -220,39 +298,63 @@
     <t>01-01-2016</t>
   </si>
   <si>
+    <t>ROMNC10004</t>
+  </si>
+  <si>
     <t>Can Love Happen Twice?</t>
   </si>
   <si>
     <t>01-01-2011</t>
   </si>
   <si>
+    <t>ROMNC10005</t>
+  </si>
+  <si>
     <t>The 3 Mistakes of My Life</t>
   </si>
   <si>
     <t>01-05-2008</t>
   </si>
   <si>
+    <t>ROMNC10006</t>
+  </si>
+  <si>
     <t>Our Impossible Love</t>
   </si>
   <si>
     <t>01-01-2017</t>
   </si>
   <si>
+    <t>ROMNC10007</t>
+  </si>
+  <si>
     <t>Like It Happened Yesterday</t>
   </si>
   <si>
     <t>05-08-2013</t>
   </si>
   <si>
+    <t>ROMNC10008</t>
+  </si>
+  <si>
     <t>You Were My Crush</t>
   </si>
   <si>
+    <t>ROMNC10009</t>
+  </si>
+  <si>
     <t>Will You Still Love Me?</t>
   </si>
   <si>
+    <t>ROMNC10010</t>
+  </si>
+  <si>
     <t>Perfect Us</t>
   </si>
   <si>
+    <t>BIOGR10001</t>
+  </si>
+  <si>
     <t>Wings of Fire</t>
   </si>
   <si>
@@ -262,6 +364,9 @@
     <t>01-01-1999</t>
   </si>
   <si>
+    <t>BIOGR10002</t>
+  </si>
+  <si>
     <t>An Autobiography</t>
   </si>
   <si>
@@ -271,6 +376,9 @@
     <t>01-01-1936</t>
   </si>
   <si>
+    <t>BIOGR10003</t>
+  </si>
+  <si>
     <t>Playing It My Way</t>
   </si>
   <si>
@@ -280,6 +388,9 @@
     <t>01-12-2014</t>
   </si>
   <si>
+    <t>BIOGR10004</t>
+  </si>
+  <si>
     <t>The Story of My Experiments with Truth</t>
   </si>
   <si>
@@ -292,6 +403,9 @@
     <t>01-01-1927</t>
   </si>
   <si>
+    <t>BIOGR10005</t>
+  </si>
+  <si>
     <t>The Insider</t>
   </si>
   <si>
@@ -301,6 +415,9 @@
     <t>01-01-1998</t>
   </si>
   <si>
+    <t>BIOGR10006</t>
+  </si>
+  <si>
     <t>A Century Is Not Enough</t>
   </si>
   <si>
@@ -310,6 +427,9 @@
     <t>24-02-2018</t>
   </si>
   <si>
+    <t>BIOGR10007</t>
+  </si>
+  <si>
     <t>The Race of My Life</t>
   </si>
   <si>
@@ -319,6 +439,9 @@
     <t>01-01-2013</t>
   </si>
   <si>
+    <t>BIOGR10008</t>
+  </si>
+  <si>
     <t>One Life is Not Enough</t>
   </si>
   <si>
@@ -328,12 +451,18 @@
     <t>01-01-2014</t>
   </si>
   <si>
+    <t>BIOGR10009</t>
+  </si>
+  <si>
     <t>281 and Beyond</t>
   </si>
   <si>
     <t>V.V.S. Laxman</t>
   </si>
   <si>
+    <t>BIOGR10010</t>
+  </si>
+  <si>
     <t>My Country My Life</t>
   </si>
   <si>
@@ -343,6 +472,9 @@
     <t>01-01-2008</t>
   </si>
   <si>
+    <t>HIS10001</t>
+  </si>
+  <si>
     <t>India After Gandhi</t>
   </si>
   <si>
@@ -352,24 +484,36 @@
     <t>20-04-2007</t>
   </si>
   <si>
+    <t>HIS10002</t>
+  </si>
+  <si>
     <t>The Discovery of India</t>
   </si>
   <si>
     <t>01-01-1946</t>
   </si>
   <si>
+    <t>HIS10003</t>
+  </si>
+  <si>
     <t>Land of the Seven Rivers</t>
   </si>
   <si>
     <t>Sanjeev Sanyal</t>
   </si>
   <si>
+    <t>HIS10004</t>
+  </si>
+  <si>
     <t>Inglorious Empire</t>
   </si>
   <si>
     <t>Shashi Tharoor</t>
   </si>
   <si>
+    <t>HIS10005</t>
+  </si>
+  <si>
     <t>The Anarchy</t>
   </si>
   <si>
@@ -379,15 +523,24 @@
     <t>01-09-2019</t>
   </si>
   <si>
+    <t>HIS10006</t>
+  </si>
+  <si>
     <t>City of Djinns</t>
   </si>
   <si>
     <t>01-01-1993</t>
   </si>
   <si>
+    <t>HIS10007</t>
+  </si>
+  <si>
     <t>The Ocean of Churn</t>
   </si>
   <si>
+    <t>HIS10008</t>
+  </si>
+  <si>
     <t>India Unbound</t>
   </si>
   <si>
@@ -397,6 +550,9 @@
     <t>01-01-2000</t>
   </si>
   <si>
+    <t>HIS10009</t>
+  </si>
+  <si>
     <t>Early India</t>
   </si>
   <si>
@@ -406,12 +562,18 @@
     <t>01-01-2002</t>
   </si>
   <si>
+    <t>HIS10010</t>
+  </si>
+  <si>
     <t>A History of India</t>
   </si>
   <si>
     <t>01-01-1966</t>
   </si>
   <si>
+    <t>NOV10001</t>
+  </si>
+  <si>
     <t>The God of Small Things</t>
   </si>
   <si>
@@ -421,6 +583,9 @@
     <t>01-01-1997</t>
   </si>
   <si>
+    <t>NOV10002</t>
+  </si>
+  <si>
     <t>Train to Pakistan</t>
   </si>
   <si>
@@ -430,18 +595,27 @@
     <t>01-01-1956</t>
   </si>
   <si>
+    <t>NOV10003</t>
+  </si>
+  <si>
     <t>A Suitable Boy</t>
   </si>
   <si>
     <t>Vikram Seth</t>
   </si>
   <si>
+    <t>NOV10004</t>
+  </si>
+  <si>
     <t>The White Tiger</t>
   </si>
   <si>
     <t>Aravind Adiga</t>
   </si>
   <si>
+    <t>NOV10005</t>
+  </si>
+  <si>
     <t>Midnight's Children</t>
   </si>
   <si>
@@ -451,6 +625,9 @@
     <t>01-01-1981</t>
   </si>
   <si>
+    <t>NOV10006</t>
+  </si>
+  <si>
     <t>The Shadow Lines</t>
   </si>
   <si>
@@ -460,6 +637,9 @@
     <t>01-01-1988</t>
   </si>
   <si>
+    <t>NOV10007</t>
+  </si>
+  <si>
     <t>Clear Light of Day</t>
   </si>
   <si>
@@ -469,12 +649,18 @@
     <t>01-01-1980</t>
   </si>
   <si>
+    <t>NOV10008</t>
+  </si>
+  <si>
     <t>The Great Indian Novel</t>
   </si>
   <si>
     <t>01-01-1989</t>
   </si>
   <si>
+    <t>NOV10009</t>
+  </si>
+  <si>
     <t>The Lowland</t>
   </si>
   <si>
@@ -484,21 +670,33 @@
     <t>27-09-2013</t>
   </si>
   <si>
+    <t>NOV10010</t>
+  </si>
+  <si>
     <t>Sea of Poppies</t>
   </si>
   <si>
+    <t>ECOCIV10001</t>
+  </si>
+  <si>
     <t>Indian Economy</t>
   </si>
   <si>
     <t>Ramesh Singh</t>
   </si>
   <si>
+    <t>ECOCIV10002</t>
+  </si>
+  <si>
     <t>A Brief History of Modern India</t>
   </si>
   <si>
     <t>Rajiv Ahir</t>
   </si>
   <si>
+    <t>ECOCIV10003</t>
+  </si>
+  <si>
     <t>The India Way</t>
   </si>
   <si>
@@ -508,45 +706,69 @@
     <t>01-01-2020</t>
   </si>
   <si>
+    <t>ECOCIV10004</t>
+  </si>
+  <si>
     <t>Indian Polity</t>
   </si>
   <si>
     <t>M. Laxmikanth</t>
   </si>
   <si>
+    <t>ECOCIV10005</t>
+  </si>
+  <si>
     <t>Certificate Physical and Human Geography</t>
   </si>
   <si>
     <t>G.C. Leong</t>
   </si>
   <si>
+    <t>ECOCIV10006</t>
+  </si>
+  <si>
     <t>Fault Lines</t>
   </si>
   <si>
     <t>Raghuram Rajan</t>
   </si>
   <si>
+    <t>ECOCIV10007</t>
+  </si>
+  <si>
     <t>I Do What I Do</t>
   </si>
   <si>
+    <t>ECOCIV10008</t>
+  </si>
+  <si>
     <t>The Made-in-India Manager</t>
   </si>
   <si>
     <t>R. Gopalakrishnan</t>
   </si>
   <si>
+    <t>ECOCIV10009</t>
+  </si>
+  <si>
     <t>Turnaround India</t>
   </si>
   <si>
     <t>R.P. Gupta</t>
   </si>
   <si>
+    <t>ECOCIV10010</t>
+  </si>
+  <si>
     <t>Why Bharat Matters</t>
   </si>
   <si>
     <t>01-01-2024</t>
   </si>
   <si>
+    <t>POET10001</t>
+  </si>
+  <si>
     <t>Gitanjali</t>
   </si>
   <si>
@@ -559,6 +781,9 @@
     <t>01-01-1910</t>
   </si>
   <si>
+    <t>POET10002</t>
+  </si>
+  <si>
     <t>Madhushala</t>
   </si>
   <si>
@@ -571,12 +796,18 @@
     <t>01-01-1935</t>
   </si>
   <si>
+    <t>POET10003</t>
+  </si>
+  <si>
     <t>Selected Poems</t>
   </si>
   <si>
     <t>Gulzar</t>
   </si>
   <si>
+    <t>POET10004</t>
+  </si>
+  <si>
     <t>Golden Threshold</t>
   </si>
   <si>
@@ -586,12 +817,18 @@
     <t>01-01-1905</t>
   </si>
   <si>
+    <t>POET10005</t>
+  </si>
+  <si>
     <t>Kamayani</t>
   </si>
   <si>
     <t>Jaishankar Prasad</t>
   </si>
   <si>
+    <t>POET10006</t>
+  </si>
+  <si>
     <t>Rashmirathi</t>
   </si>
   <si>
@@ -601,6 +838,9 @@
     <t>01-01-1952</t>
   </si>
   <si>
+    <t>POET10007</t>
+  </si>
+  <si>
     <t>Diwan-e-Ghalib</t>
   </si>
   <si>
@@ -613,12 +853,18 @@
     <t>01-01-1841</t>
   </si>
   <si>
+    <t>POET10008</t>
+  </si>
+  <si>
     <t>The Collected Poems</t>
   </si>
   <si>
     <t>01-01-1985</t>
   </si>
   <si>
+    <t>POET10009</t>
+  </si>
+  <si>
     <t>Summer in Calcutta</t>
   </si>
   <si>
@@ -628,12 +874,18 @@
     <t>01-01-1965</t>
   </si>
   <si>
+    <t>POET10010</t>
+  </si>
+  <si>
     <t>Stray Birds</t>
   </si>
   <si>
     <t>01-01-1916</t>
   </si>
   <si>
+    <t>POLYSC10001</t>
+  </si>
+  <si>
     <t>The Argumentative Indian</t>
   </si>
   <si>
@@ -643,18 +895,30 @@
     <t>01-01-2005</t>
   </si>
   <si>
+    <t>POLYSC10002</t>
+  </si>
+  <si>
     <t>Annihilation of Caste</t>
   </si>
   <si>
     <t>B.R. Ambedkar</t>
   </si>
   <si>
+    <t>POLYSC10003</t>
+  </si>
+  <si>
     <t>An Era of Darkness</t>
   </si>
   <si>
+    <t>POLYSC10004</t>
+  </si>
+  <si>
     <t>The Paradoxical Prime Minister</t>
   </si>
   <si>
+    <t>POLYSC10005</t>
+  </si>
+  <si>
     <t>How India Votes</t>
   </si>
   <si>
@@ -664,39 +928,60 @@
     <t>01-01-2019</t>
   </si>
   <si>
+    <t>POLYSC10006</t>
+  </si>
+  <si>
     <t>To Kill a Democracy</t>
   </si>
   <si>
     <t>Debasish Roy Chowdhury</t>
   </si>
   <si>
+    <t>POLYSC10007</t>
+  </si>
+  <si>
     <t>Seeing Like a Feminist</t>
   </si>
   <si>
     <t>Nivedita Menon</t>
   </si>
   <si>
+    <t>POLYSC10008</t>
+  </si>
+  <si>
     <t>Malevolent Republic</t>
   </si>
   <si>
     <t>K.S. Komireddi</t>
   </si>
   <si>
+    <t>POLYSC10009</t>
+  </si>
+  <si>
     <t>The Battle of Belonging</t>
   </si>
   <si>
+    <t>POLYSC10010</t>
+  </si>
+  <si>
     <t>In Spite of the Gods</t>
   </si>
   <si>
     <t>Edward Luce</t>
   </si>
   <si>
+    <t>MOTV10001</t>
+  </si>
+  <si>
     <t>Life's Amazing Secrets</t>
   </si>
   <si>
     <t>Gaur Gopal Das</t>
   </si>
   <si>
+    <t>MOTV10002</t>
+  </si>
+  <si>
     <t>Think Like a Monk</t>
   </si>
   <si>
@@ -706,6 +991,9 @@
     <t>08-09-2020</t>
   </si>
   <si>
+    <t>MOTV10003</t>
+  </si>
+  <si>
     <t>The 5 AM Club</t>
   </si>
   <si>
@@ -715,21 +1003,36 @@
     <t>04-12-2018</t>
   </si>
   <si>
+    <t>MOTV10004</t>
+  </si>
+  <si>
     <t>The Monk Who Sold His Ferrari</t>
   </si>
   <si>
+    <t>MOTV10005</t>
+  </si>
+  <si>
     <t>Who Will Cry When You Die?</t>
   </si>
   <si>
+    <t>MOTV10006</t>
+  </si>
+  <si>
     <t>Karma: A Yogi's Guide to Crafting Your Destiny</t>
   </si>
   <si>
     <t>Sadhguru</t>
   </si>
   <si>
+    <t>MOTV10007</t>
+  </si>
+  <si>
     <t>Inner Engineering</t>
   </si>
   <si>
+    <t>MOTV10008</t>
+  </si>
+  <si>
     <t>Don't Lose Your Mind, Lose Your Weight</t>
   </si>
   <si>
@@ -739,325 +1042,22 @@
     <t>01-01-2009</t>
   </si>
   <si>
+    <t>MOTV10009</t>
+  </si>
+  <si>
     <t>The Rudest Book Ever</t>
   </si>
   <si>
     <t>Shwetabh Gangwar</t>
   </si>
   <si>
+    <t>MOTV10010</t>
+  </si>
+  <si>
     <t>Energize Your Mind</t>
   </si>
   <si>
     <t>01-01-2022</t>
-  </si>
-  <si>
-    <t>MYTH10001</t>
-  </si>
-  <si>
-    <t>MYTH10002</t>
-  </si>
-  <si>
-    <t>MYTH10003</t>
-  </si>
-  <si>
-    <t>MYTH10004</t>
-  </si>
-  <si>
-    <t>MYTH10005</t>
-  </si>
-  <si>
-    <t>MYTH10006</t>
-  </si>
-  <si>
-    <t>MYTH10007</t>
-  </si>
-  <si>
-    <t>MYTH10008</t>
-  </si>
-  <si>
-    <t>MYTH10009</t>
-  </si>
-  <si>
-    <t>MYTH10010</t>
-  </si>
-  <si>
-    <t>CRIMYS10001</t>
-  </si>
-  <si>
-    <t>CRIMYS10002</t>
-  </si>
-  <si>
-    <t>CRIMYS10003</t>
-  </si>
-  <si>
-    <t>CRIMYS10004</t>
-  </si>
-  <si>
-    <t>CRIMYS10005</t>
-  </si>
-  <si>
-    <t>CRIMYS10006</t>
-  </si>
-  <si>
-    <t>CRIMYS10007</t>
-  </si>
-  <si>
-    <t>CRIMYS10008</t>
-  </si>
-  <si>
-    <t>CRIMYS10009</t>
-  </si>
-  <si>
-    <t>CRIMYS10010</t>
-  </si>
-  <si>
-    <t>Charges per day (Rs)</t>
-  </si>
-  <si>
-    <t>ROMNC10001</t>
-  </si>
-  <si>
-    <t>ROMNC10002</t>
-  </si>
-  <si>
-    <t>ROMNC10003</t>
-  </si>
-  <si>
-    <t>ROMNC10004</t>
-  </si>
-  <si>
-    <t>ROMNC10005</t>
-  </si>
-  <si>
-    <t>ROMNC10006</t>
-  </si>
-  <si>
-    <t>ROMNC10007</t>
-  </si>
-  <si>
-    <t>ROMNC10008</t>
-  </si>
-  <si>
-    <t>ROMNC10009</t>
-  </si>
-  <si>
-    <t>ROMNC10010</t>
-  </si>
-  <si>
-    <t>Market Price (INR)</t>
-  </si>
-  <si>
-    <t>Quantities Available</t>
-  </si>
-  <si>
-    <t>BIOGR10001</t>
-  </si>
-  <si>
-    <t>BIOGR10002</t>
-  </si>
-  <si>
-    <t>BIOGR10003</t>
-  </si>
-  <si>
-    <t>BIOGR10004</t>
-  </si>
-  <si>
-    <t>BIOGR10005</t>
-  </si>
-  <si>
-    <t>BIOGR10006</t>
-  </si>
-  <si>
-    <t>BIOGR10007</t>
-  </si>
-  <si>
-    <t>BIOGR10008</t>
-  </si>
-  <si>
-    <t>BIOGR10009</t>
-  </si>
-  <si>
-    <t>BIOGR10010</t>
-  </si>
-  <si>
-    <t>HIS10001</t>
-  </si>
-  <si>
-    <t>HIS10002</t>
-  </si>
-  <si>
-    <t>HIS10003</t>
-  </si>
-  <si>
-    <t>HIS10004</t>
-  </si>
-  <si>
-    <t>HIS10005</t>
-  </si>
-  <si>
-    <t>HIS10006</t>
-  </si>
-  <si>
-    <t>HIS10007</t>
-  </si>
-  <si>
-    <t>HIS10008</t>
-  </si>
-  <si>
-    <t>HIS10009</t>
-  </si>
-  <si>
-    <t>HIS10010</t>
-  </si>
-  <si>
-    <t>NOV10001</t>
-  </si>
-  <si>
-    <t>NOV10002</t>
-  </si>
-  <si>
-    <t>NOV10003</t>
-  </si>
-  <si>
-    <t>NOV10004</t>
-  </si>
-  <si>
-    <t>NOV10005</t>
-  </si>
-  <si>
-    <t>NOV10006</t>
-  </si>
-  <si>
-    <t>NOV10007</t>
-  </si>
-  <si>
-    <t>NOV10008</t>
-  </si>
-  <si>
-    <t>NOV10009</t>
-  </si>
-  <si>
-    <t>NOV10010</t>
-  </si>
-  <si>
-    <t>ECOCIV10001</t>
-  </si>
-  <si>
-    <t>ECOCIV10002</t>
-  </si>
-  <si>
-    <t>ECOCIV10003</t>
-  </si>
-  <si>
-    <t>ECOCIV10004</t>
-  </si>
-  <si>
-    <t>ECOCIV10005</t>
-  </si>
-  <si>
-    <t>ECOCIV10006</t>
-  </si>
-  <si>
-    <t>ECOCIV10007</t>
-  </si>
-  <si>
-    <t>ECOCIV10008</t>
-  </si>
-  <si>
-    <t>ECOCIV10009</t>
-  </si>
-  <si>
-    <t>ECOCIV10010</t>
-  </si>
-  <si>
-    <t>POET10001</t>
-  </si>
-  <si>
-    <t>POET10002</t>
-  </si>
-  <si>
-    <t>POET10003</t>
-  </si>
-  <si>
-    <t>POET10004</t>
-  </si>
-  <si>
-    <t>POET10005</t>
-  </si>
-  <si>
-    <t>POET10006</t>
-  </si>
-  <si>
-    <t>POET10007</t>
-  </si>
-  <si>
-    <t>POET10008</t>
-  </si>
-  <si>
-    <t>POET10009</t>
-  </si>
-  <si>
-    <t>POET10010</t>
-  </si>
-  <si>
-    <t>POLYSC10001</t>
-  </si>
-  <si>
-    <t>POLYSC10002</t>
-  </si>
-  <si>
-    <t>POLYSC10003</t>
-  </si>
-  <si>
-    <t>POLYSC10004</t>
-  </si>
-  <si>
-    <t>POLYSC10005</t>
-  </si>
-  <si>
-    <t>POLYSC10006</t>
-  </si>
-  <si>
-    <t>POLYSC10007</t>
-  </si>
-  <si>
-    <t>POLYSC10008</t>
-  </si>
-  <si>
-    <t>POLYSC10009</t>
-  </si>
-  <si>
-    <t>POLYSC10010</t>
-  </si>
-  <si>
-    <t>MOTV10001</t>
-  </si>
-  <si>
-    <t>MOTV10002</t>
-  </si>
-  <si>
-    <t>MOTV10003</t>
-  </si>
-  <si>
-    <t>MOTV10004</t>
-  </si>
-  <si>
-    <t>MOTV10005</t>
-  </si>
-  <si>
-    <t>MOTV10006</t>
-  </si>
-  <si>
-    <t>MOTV10007</t>
-  </si>
-  <si>
-    <t>MOTV10008</t>
-  </si>
-  <si>
-    <t>MOTV10009</t>
-  </si>
-  <si>
-    <t>MOTV10010</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1067,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1079,12 +1079,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1133,7 +1127,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1481,13 +1475,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1495,19 +1489,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3">
         <v>250</v>
@@ -1516,7 +1510,7 @@
         <v>23</v>
       </c>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>10</v>
       </c>
     </row>
@@ -1525,19 +1519,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3">
         <v>350</v>
@@ -1546,7 +1540,7 @@
         <v>34</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -1555,19 +1549,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>290</v>
@@ -1585,19 +1579,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>243</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G5" s="3">
         <v>310</v>
@@ -1615,19 +1609,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3">
         <v>275</v>
@@ -1645,19 +1639,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G7" s="3">
         <v>350</v>
@@ -1675,19 +1669,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>246</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3">
         <v>399</v>
@@ -1705,19 +1699,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3">
         <v>399</v>
@@ -1735,19 +1729,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>248</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3">
         <v>350</v>
@@ -1765,19 +1759,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>249</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3">
         <v>295</v>
@@ -1791,7 +1785,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1832,13 +1825,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1846,26 +1839,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3">
         <v>250</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>10</v>
       </c>
     </row>
@@ -1874,26 +1867,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>223</v>
+        <v>318</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>224</v>
+        <v>319</v>
       </c>
       <c r="G3" s="3">
         <v>399</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -1902,26 +1895,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>225</v>
+        <v>321</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>227</v>
+        <v>323</v>
       </c>
       <c r="G4" s="3">
         <v>299</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <f>ROUND(G4*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -1930,19 +1923,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="G5" s="3">
         <v>225</v>
@@ -1958,19 +1951,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="G6" s="3">
         <v>199</v>
@@ -1986,19 +1979,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>230</v>
+        <v>329</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3">
         <v>299</v>
@@ -2014,19 +2007,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>232</v>
+        <v>332</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3">
         <v>325</v>
@@ -2042,19 +2035,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>233</v>
+        <v>334</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>234</v>
+        <v>335</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>235</v>
+        <v>336</v>
       </c>
       <c r="G9" s="3">
         <v>250</v>
@@ -2070,19 +2063,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>236</v>
+        <v>338</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="G10" s="3">
         <v>299</v>
@@ -2098,19 +2091,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="G11" s="3">
         <v>299</v>
@@ -2122,7 +2115,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2163,13 +2155,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2177,26 +2169,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3">
         <v>299</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>12</v>
       </c>
     </row>
@@ -2205,26 +2197,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G3" s="3">
         <v>599</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -2233,19 +2225,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>252</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G4" s="3">
         <v>320</v>
@@ -2261,19 +2253,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G5" s="3">
         <v>350</v>
@@ -2289,19 +2281,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>254</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3">
         <v>299</v>
@@ -2317,19 +2309,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G7" s="3">
         <v>350</v>
@@ -2345,19 +2337,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G8" s="3">
         <v>399</v>
@@ -2373,19 +2365,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>257</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3">
         <v>399</v>
@@ -2401,19 +2393,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>258</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3">
         <v>250</v>
@@ -2429,19 +2421,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>259</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3">
         <v>299</v>
@@ -2453,7 +2445,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2494,13 +2485,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2508,26 +2499,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G2" s="3">
         <v>199</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -2536,26 +2527,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3">
         <v>175</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -2564,19 +2555,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>263</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3">
         <v>199</v>
@@ -2592,19 +2583,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3">
         <v>199</v>
@@ -2620,19 +2611,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="G6" s="3">
         <v>199</v>
@@ -2648,19 +2639,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>266</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3">
         <v>199</v>
@@ -2676,19 +2667,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>267</v>
+        <v>98</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>199</v>
@@ -2704,19 +2695,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3">
         <v>175</v>
@@ -2732,19 +2723,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="G10" s="3">
         <v>220</v>
@@ -2760,19 +2751,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G11" s="3">
         <v>249</v>
@@ -2784,7 +2775,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2825,13 +2815,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2839,26 +2829,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>273</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="G2" s="3">
         <v>225</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>9</v>
       </c>
     </row>
@@ -2867,26 +2857,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>274</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3">
         <v>450</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
@@ -2895,19 +2885,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>275</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="G4" s="3">
         <v>499</v>
@@ -2923,19 +2913,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>276</v>
+        <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="G5" s="3">
         <v>150</v>
@@ -2951,19 +2941,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>277</v>
+        <v>124</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="G6" s="3">
         <v>599</v>
@@ -2979,19 +2969,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="G7" s="3">
         <v>399</v>
@@ -3007,19 +2997,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="G8" s="3">
         <v>250</v>
@@ -3035,19 +3025,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>280</v>
+        <v>136</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="G9" s="3">
         <v>400</v>
@@ -3063,19 +3053,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G10" s="3">
         <v>450</v>
@@ -3091,19 +3081,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>282</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G11" s="3">
         <v>550</v>
@@ -3115,7 +3105,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3156,13 +3145,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -3170,26 +3159,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="G2" s="3">
         <v>650</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>26</v>
       </c>
     </row>
@@ -3198,26 +3187,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="G3" s="3">
         <v>499</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -3226,26 +3215,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>154</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3">
         <v>350</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <f>ROUND(G4*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -3254,19 +3243,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3">
         <v>499</v>
@@ -3282,19 +3271,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>287</v>
+        <v>160</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="G6" s="3">
         <v>699</v>
@@ -3310,19 +3299,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>288</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="G7" s="3">
         <v>399</v>
@@ -3338,19 +3327,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>289</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3">
         <v>399</v>
@@ -3366,19 +3355,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>290</v>
+        <v>169</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="G9" s="3">
         <v>450</v>
@@ -3394,19 +3383,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>291</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="G10" s="3">
         <v>550</v>
@@ -3422,19 +3411,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>292</v>
+        <v>177</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="G11" s="3">
         <v>399</v>
@@ -3446,7 +3435,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3487,13 +3475,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -3501,26 +3489,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>293</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="G2" s="3">
         <v>325</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -3529,26 +3517,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>294</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="G3" s="3">
         <v>194</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -3557,26 +3545,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="G4" s="3">
         <v>799</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <f>ROUND(G4*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -3585,19 +3573,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>296</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G5" s="3">
         <v>350</v>
@@ -3613,19 +3601,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>297</v>
+        <v>194</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="G6" s="3">
         <v>499</v>
@@ -3641,19 +3629,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="G7" s="3">
         <v>299</v>
@@ -3669,19 +3657,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="G8" s="3">
         <v>320</v>
@@ -3697,19 +3685,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>147</v>
+        <v>208</v>
       </c>
       <c r="G9" s="3">
         <v>399</v>
@@ -3725,19 +3713,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="G10" s="3">
         <v>399</v>
@@ -3753,19 +3741,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G11" s="3">
         <v>450</v>
@@ -3777,7 +3765,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3818,13 +3805,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -3832,26 +3819,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>303</v>
+        <v>215</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="G2" s="3">
         <v>595</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>24</v>
       </c>
     </row>
@@ -3860,26 +3847,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3">
         <v>310</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -3888,26 +3875,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>305</v>
+        <v>221</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>222</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="G4" s="3">
         <v>499</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <f>ROUND(G4*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -3916,19 +3903,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="G5" s="3">
         <v>725</v>
@@ -3944,19 +3931,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>307</v>
+        <v>228</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="G6" s="3">
         <v>330</v>
@@ -3972,19 +3959,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>308</v>
+        <v>231</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3">
         <v>499</v>
@@ -4000,19 +3987,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3">
         <v>450</v>
@@ -4028,19 +4015,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="G9" s="3">
         <v>399</v>
@@ -4056,19 +4043,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3">
         <v>299</v>
@@ -4084,19 +4071,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>170</v>
+        <v>243</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="G11" s="3">
         <v>550</v>
@@ -4108,7 +4095,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4149,13 +4135,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4163,26 +4149,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>313</v>
+        <v>245</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="G2" s="3">
         <v>125</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3">
-        <f>ROUND(G2*4%,0)</f>
+        <f t="shared" ref="I2:I11" si="0">ROUND(G2*4%,0)</f>
         <v>5</v>
       </c>
     </row>
@@ -4191,26 +4177,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>314</v>
+        <v>250</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>179</v>
+        <v>254</v>
       </c>
       <c r="G3" s="3">
         <v>150</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="0">ROUND(G3*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -4219,26 +4205,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="G4" s="3">
         <v>299</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3">
-        <f>ROUND(G4*4%,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -4247,19 +4233,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
+        <v>259</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="G5" s="3">
         <v>110</v>
@@ -4275,19 +4261,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3">
         <v>175</v>
@@ -4303,19 +4289,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>187</v>
+        <v>266</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="G7" s="3">
         <v>140</v>
@@ -4331,19 +4317,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="G8" s="3">
         <v>199</v>
@@ -4359,19 +4345,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>194</v>
+        <v>275</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>195</v>
+        <v>276</v>
       </c>
       <c r="G9" s="3">
         <v>499</v>
@@ -4387,19 +4373,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="G10" s="3">
         <v>220</v>
@@ -4415,19 +4401,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="G11" s="3">
         <v>125</v>
@@ -4439,7 +4425,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4480,13 +4465,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4494,19 +4479,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>323</v>
+        <v>284</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>201</v>
+        <v>285</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="G2" s="3">
         <v>399</v>
@@ -4519,19 +4504,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3">
         <v>190</v>
@@ -4544,19 +4529,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>292</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3">
         <v>380</v>
@@ -4569,19 +4554,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3">
         <v>550</v>
@@ -4594,19 +4579,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="G6" s="3">
         <v>450</v>
@@ -4619,19 +4604,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>211</v>
+        <v>300</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>212</v>
+        <v>301</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="G7" s="3">
         <v>499</v>
@@ -4644,19 +4629,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3">
         <v>350</v>
@@ -4669,19 +4654,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>216</v>
+        <v>307</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="G9" s="3">
         <v>499</v>
@@ -4694,19 +4679,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="G10" s="3">
         <v>450</v>
@@ -4719,19 +4704,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>218</v>
+        <v>311</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>219</v>
+        <v>312</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3">
         <v>399</v>
@@ -4740,7 +4725,6 @@
       <c r="I11" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>